--- a/artfynd/A 33366-2023 artfynd.xlsx
+++ b/artfynd/A 33366-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33366-2023 artfynd.xlsx
+++ b/artfynd/A 33366-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>111835718</v>
       </c>
       <c r="B3" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>111835826</v>
       </c>
       <c r="B4" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33366-2023 artfynd.xlsx
+++ b/artfynd/A 33366-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>111835718</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>111835826</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33366-2023 artfynd.xlsx
+++ b/artfynd/A 33366-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111835758</v>
       </c>
       <c r="B2" t="n">
-        <v>77550</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +713,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471087</v>
+        <v>471088</v>
       </c>
       <c r="R2" t="n">
         <v>6810391</v>
@@ -781,47 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111835718</v>
+        <v>111835745</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471101</v>
+        <v>471153</v>
       </c>
       <c r="R3" t="n">
-        <v>6810412</v>
+        <v>6810381</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111835826</v>
+        <v>133709013</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,45 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storberget-Tjåbergsreservatet, Dlr</t>
+          <t>Svedvasseltjärnen, Svedvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470916</v>
+        <v>471120</v>
       </c>
       <c r="R4" t="n">
-        <v>6810386</v>
+        <v>6810444</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>även hackspettbo, troligen av tret</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,27 +962,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111835745</v>
+        <v>111835718</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,26 +985,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,13 +1017,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471153</v>
+        <v>471101</v>
       </c>
       <c r="R5" t="n">
-        <v>6810382</v>
+        <v>6810412</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1061,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111835838</v>
+        <v>111835826</v>
       </c>
       <c r="B6" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,26 +1090,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470915</v>
+        <v>470916</v>
       </c>
       <c r="R6" t="n">
-        <v>6810369</v>
+        <v>6810386</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,13 +1160,17 @@
           <t>2023-09-01</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>även hackspettbo, troligen av tret</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,15 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111835766</v>
+        <v>111835723</v>
       </c>
       <c r="B7" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,26 +1200,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,13 +1232,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471073</v>
+        <v>471101</v>
       </c>
       <c r="R7" t="n">
-        <v>6810389</v>
+        <v>6810412</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1276,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33366-2023 artfynd.xlsx
+++ b/artfynd/A 33366-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111835758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111835745</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133709013</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111835718</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111835826</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,8 +1321,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111835723</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>